--- a/results/log_pv_cap_per_inst_fit/log_pv_cap_per_inst_fit_densities_adensity_estimates.xlsx
+++ b/results/log_pv_cap_per_inst_fit/log_pv_cap_per_inst_fit_densities_adensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap_per_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap_per_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap_per_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap_per_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap_per_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap_per_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_cap_per_inst_fit ~ (densities): adensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>adensity</t>
+          <t>D(Firm assets)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>-0.000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.155***</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.072***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.072***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.072***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.145***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.145***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.145***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -704,36 +614,6 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.003**</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-0.003**</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-0.003**</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
@@ -742,7 +622,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,121 +668,91 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>-0.047***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.109***</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-0.109***</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.109***</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.052***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.052***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.052***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_adensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.658***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.199***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.114***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.601***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.228***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.133***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>-0.025</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.041+</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.044*</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.709***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.201***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.117***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Firm assets))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>0.041+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.028*</t>
+          <t>0.044*</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_cap_per_inst_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.658***</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.199***</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.114***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.601***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.228***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.133***</t>
-        </is>
-      </c>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.206</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.217</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.206</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.203</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.190</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.190</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.190</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
+          <t>-0.028*</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-14735.961</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-14704.672</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-14706.308</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-14740.094</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-14706.902</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-14704.185</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-14738.168</t>
+          <t>0.190</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-14699.577</t>
+          <t>0.190</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14698.993</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-7626.485</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-7626.485</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>-7626.485</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-7513.369</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>-7513.369</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-7513.369</t>
+          <t>0.190</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-14685.218</t>
+          <t>-14735.961</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-14653.928</t>
+          <t>-14704.672</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-14655.564</t>
+          <t>-14706.308</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-14711.903</t>
+          <t>-14740.094</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-14678.711</t>
+          <t>-14706.902</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-14675.994</t>
+          <t>-14704.185</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-14715.615</t>
+          <t>-14738.168</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-14677.024</t>
+          <t>-14699.577</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14676.441</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>-7598.294</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-7598.294</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>-7598.294</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-7485.178</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>-7485.178</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>-7485.178</t>
+          <t>-14698.993</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7376.981</t>
+          <t>-14685.218</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7361.336</t>
+          <t>-14653.928</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7362.154</t>
+          <t>-14655.564</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7375.047</t>
+          <t>-14711.903</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7358.451</t>
+          <t>-14678.711</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7357.092</t>
+          <t>-14675.994</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7373.084</t>
+          <t>-14715.615</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7353.789</t>
+          <t>-14677.024</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7353.497</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>3818.243</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>3818.243</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>3818.243</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>3761.685</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>3761.685</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>3761.685</t>
+          <t>-14676.441</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7376.981</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7361.336</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7362.154</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7375.047</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7358.451</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7357.092</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7373.084</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7353.789</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>7353.497</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.667799   1  0.000000
-1  LM Marginal Spatial (LM2)     0.182555   1  0.427574
-2             LM Joint (LMJ)  4715.300014   2  0.000000</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.667799   1  0.000000
-1  LM Marginal Spatial (LM2)    -1.855763   1  0.968256
-2             LM Joint (LMJ)  4715.266687   2  0.000000</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.667799   1  0.000000
-1  LM Marginal Spatial (LM2)    -2.858157   1  0.997869
-2             LM Joint (LMJ)  4715.266687   2  0.000000</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df  p-value
-0      LM Conditional Spatial  13.718749  1      0.0
-1  Hausman Specification Test  28.413785  4  0.00001</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df   p-value
-0      LM Conditional Spatial   4.237462  1  0.000011
-1  Hausman Specification Test  28.413785  4   0.00001</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df  p-value
-0      LM Conditional Spatial   5.148354  1      0.0
-1  Hausman Specification Test  28.413785  4  0.00001</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   adensity          0.0  0.000001  0.157201  0.875086
-1                 log_income     0.097803  0.022423  4.361718  0.000013
-2                 log_hholds     -0.00021  0.000364  -0.57619  0.564487
-3            log_sunny_hours    -0.042897  0.010526 -4.075264  0.000046
-4                 W_adensity    -0.000001  0.000017 -0.043242  0.965509
-5               W_log_income    -0.025059  0.032555 -0.769741  0.441454
-6               W_log_hholds     -0.00266  0.004873 -0.545795  0.585207
-7          W_log_sunny_hours     0.018184  0.015822  1.149307  0.250429
-8  W_log_pv_cap_per_inst_fit     0.657504  0.086689  7.584589       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   adensity         -0.0  0.000001 -0.098243  0.921739
-1                 log_income     0.093248  0.021515  4.334033  0.000015
-2                 log_hholds    -0.000275  0.000367 -0.750681  0.452845
-3            log_sunny_hours     -0.04257  0.010035 -4.242245  0.000022
-4                 W_adensity         -0.0  0.000002 -0.142366  0.886791
-5               W_log_income     0.040653  0.024075  1.688623  0.091292
-6               W_log_hholds     0.001385  0.001084  1.277818  0.201313
-7          W_log_sunny_hours    -0.008213  0.013147 -0.624746  0.532138
-8  W_log_pv_cap_per_inst_fit     0.199243  0.041303  4.823971  0.000001</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   adensity          0.0  0.000001  0.015805   0.98739
-1                 log_income     0.102391  0.020432  5.011209  0.000001
-2                 log_hholds    -0.000306  0.000366 -0.837197  0.402482
-3            log_sunny_hours    -0.033409  0.009803 -3.408123  0.000654
-4                 W_adensity     0.000001  0.000001   0.49084  0.623539
-5               W_log_income     0.044105   0.02168  2.034361  0.041915
-6               W_log_hholds     0.000251    0.0006  0.417831  0.676071
-7          W_log_sunny_hours    -0.027818  0.012212 -2.277894  0.022733
-8  W_log_pv_cap_per_inst_fit     0.114298  0.032175  3.552417  0.000382</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   adensity          0.0  0.000001   0.11989   0.90457
-1                 log_income      0.07786  0.013298  5.854895       0.0
-2                 log_hholds    -0.000241  0.000363 -0.662787  0.507467
-3            log_sunny_hours    -0.035236  0.007598 -4.637671  0.000004
-4  W_log_pv_cap_per_inst_fit     0.600636  0.069838  8.600421       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err    zt_stat      prob
-0                   adensity         -0.0  0.000001  -0.049199  0.960761
-1                 log_income      0.12761  0.008925  14.297647       0.0
-2                 log_hholds    -0.000286  0.000366   -0.78098  0.434815
-3            log_sunny_hours    -0.044651  0.007218  -6.185965       0.0
-4  W_log_pv_cap_per_inst_fit     0.227802  0.038402   5.932028       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err    zt_stat      prob
-0                   adensity          0.0  0.000001   0.008571  0.993162
-1                 log_income     0.137942  0.008343  16.534467       0.0
-2                 log_hholds      -0.0003  0.000366  -0.818725  0.412943
-3            log_sunny_hours    -0.046306  0.007202  -6.429252       0.0
-4  W_log_pv_cap_per_inst_fit     0.132613  0.030859   4.297466  0.000017</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0         adensity          0.0  0.000001  0.160452  0.872525
-1       log_income     0.136577  0.016521     8.267       0.0
-2       log_hholds    -0.000187  0.000363 -0.515927  0.605906
-3  log_sunny_hours    -0.041359   0.00996 -4.152678  0.000033
-4           lambda     0.708857  0.075588  9.377928       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         adensity         -0.0  0.000001  -0.039945  0.968137
-1       log_income     0.155539  0.008631  18.021871       0.0
-2       log_hholds    -0.000308  0.000365  -0.844133  0.398595
-3  log_sunny_hours    -0.047583  0.007971  -5.969399       0.0
-4           lambda     0.201153  0.041282   4.872681  0.000001</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         adensity         -0.0  0.000001  -0.024845  0.980178
-1       log_income      0.15479  0.007986  19.382948       0.0
-2       log_hholds     -0.00031  0.000366  -0.848717  0.396039
-3  log_sunny_hours    -0.047419  0.007646  -6.201833       0.0
-4           lambda      0.11723  0.032167   3.644392  0.000268</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0         CONSTANT     0.700544  0.058678  11.93871       0.0
-1         adensity     0.000001  0.000003  0.262476   0.79298
-2       log_income     0.072325  0.008767  8.250153       0.0
-3       log_hholds    -0.002842  0.001022 -2.781837  0.005454
-4  log_sunny_hours    -0.109323  0.018434 -5.930612       0.0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0         CONSTANT     0.700544  0.058678  11.93871       0.0
-1         adensity     0.000001  0.000003  0.262476   0.79298
-2       log_income     0.072325  0.008767  8.250153       0.0
-3       log_hholds    -0.002842  0.001022 -2.781837  0.005454
-4  log_sunny_hours    -0.109323  0.018434 -5.930612       0.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0         CONSTANT     0.700544  0.058678  11.93871       0.0
-1         adensity     0.000001  0.000003  0.262476   0.79298
-2       log_income     0.072325  0.008767  8.250153       0.0
-3       log_hholds    -0.002842  0.001022 -2.781837  0.005454
-4  log_sunny_hours    -0.109323  0.018434 -5.930612       0.0</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.191033  0.035889   5.322808       0.0
-1         adensity          0.0  0.000001   0.076924  0.938684
-2       log_income     0.145459  0.007442  19.545844       0.0
-3       log_hholds    -0.000256  0.000402  -0.636887  0.524199
-4  log_sunny_hours    -0.051793  0.007853  -6.594992       0.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.191033  0.035889   5.322808       0.0
-1         adensity          0.0  0.000001   0.076924  0.938684
-2       log_income     0.145459  0.007442  19.545844       0.0
-3       log_hholds    -0.000256  0.000402  -0.636887  0.524199
-4  log_sunny_hours    -0.051793  0.007853  -6.594992       0.0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.191033  0.035889   5.322808       0.0
-1         adensity          0.0  0.000001   0.076924  0.938684
-2       log_income     0.145459  0.007442  19.545844       0.0
-3       log_hholds    -0.000256  0.000402  -0.636887  0.524199
-4  log_sunny_hours    -0.051793  0.007853  -6.594992       0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-adensity                                    -0.000002   
-log_income                                   0.212392   
-log_hholds                                  -0.008378   
-log_sunny_hours                             -0.072156   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-adensity                                  9.964689e-08   
-log_income                                9.780256e-02   
-log_hholds                               -2.097099e-04   
-log_sunny_hours                          -4.289695e-02   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-adensity                                       -0.000002  
-log_income                                      0.114589  
-log_hholds                                     -0.008168  
-log_sunny_hours                                -0.029259  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-adensity                         -4.329551e-07   
-log_income                        1.672182e-01   
-log_hholds                        1.385468e-03   
-log_sunny_hours                  -6.341966e-02   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-adensity                          -6.265821e-08   
-log_income                         9.324809e-02   
-log_hholds                        -2.753245e-04   
-log_sunny_hours                   -4.257029e-02   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-adensity                            -3.702969e-07  
-log_income                           7.397012e-02  
-log_hholds                           1.660793e-03  
-log_sunny_hours                     -2.084938e-02  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-adensity                      6.066586e-07                1.007473e-08   
-log_income                    1.654017e-01                1.023911e-01   
-log_hholds                   -6.300749e-05               -3.064348e-04   
-log_sunny_hours              -6.912809e-02               -3.340892e-02   
-                 indirect_ML_LagFE(SLX)_queen  
-adensity                         5.965838e-07  
-log_income                       6.301064e-02  
-log_hholds                       2.434273e-04  
-log_sunny_hours                 -3.571917e-02  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-adensity                            1.900409e-07   
-log_income                          1.949594e-01   
-log_hholds                         -6.030082e-04   
-log_sunny_hours                    -8.823011e-02   
-                 direct_ML_LagFE_inverse_distance  \
-adensity                             7.589553e-08   
-log_income                           7.785979e-02   
-log_hholds                          -2.408199e-04   
-log_sunny_hours                     -3.523595e-02   
-                 indirect_ML_LagFE_inverse_distance  
-adensity                               1.141454e-07  
-log_income                             1.170996e-01  
-log_hholds                            -3.621883e-04  
-log_sunny_hours                       -5.299416e-02  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-adensity                    -4.061586e-08              -3.136347e-08   
-log_income                   1.652563e-01               1.276105e-01   
-log_hholds                  -3.699878e-04              -2.857037e-04   
-log_sunny_hours             -5.782325e-02              -4.465097e-02   
-                 indirect_ML_LagFE_k_nearest  
-adensity                       -9.252394e-09  
-log_income                      3.764579e-02  
-log_hholds                     -8.428414e-05  
-log_sunny_hours                -1.317228e-02  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-adensity                 6.309541e-09           5.472812e-09   
-log_income               1.590312e-01           1.379415e-01   
-log_hholds              -3.458744e-04          -3.000069e-04   
-log_sunny_hours         -5.338587e-02          -4.630619e-02   
-                 indirect_ML_LagFE_queen  
-adensity                    8.367294e-10  
-log_income                  2.108966e-02  
-log_hholds                 -4.586757e-05  
-log_sunny_hours            -7.079680e-03  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.709***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.201***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.117***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.701***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0.701***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>0.701***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0.191***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0.191***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>0.191***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
